--- a/examples/results/capacity_expansion_planning.xlsx
+++ b/examples/results/capacity_expansion_planning.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,36 +435,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'p_min_pu': 0.5, 'system_cost': 84.74277332985903, 'generator_capacities': Generator
+          <t>{'p_min_pu': 0.1, 'system_cost': 84.40879288553354, 'generator_capacities': Generator
 OCGT         0.000000
-onwind     288.249425
-offwind     81.419666
-solar      205.947175
+onwind     273.893836
+offwind     90.992779
+solar      200.424159
 Name: p_nom_opt, dtype: float64, 'storage_capacities': StorageUnit
-battery storage                 50.132036
-hydrogen storage underground    43.304166
+battery storage                 39.515823
+hydrogen storage underground    45.214748
 Name: p_nom_opt, dtype: float64, 'al_capacity': 6.050000000000001}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'p_min_pu': 0.9, 'system_cost': 84.94087482018166, 'generator_capacities': Generator
+          <t>{'p_min_pu': 0.5, 'system_cost': 87.13052141396358, 'generator_capacities': Generator
 OCGT         0.000000
-onwind     285.483157
-offwind     83.718497
-solar      205.626568
+onwind     262.030093
+offwind     96.068840
+solar      213.244300
 Name: p_nom_opt, dtype: float64, 'storage_capacities': StorageUnit
-battery storage                 47.785081
-hydrogen storage underground    43.449171
+battery storage                 47.106483
+hydrogen storage underground    48.706380
+Name: p_nom_opt, dtype: float64, 'al_capacity': 6.050000000000001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>{'p_min_pu': 0.9, 'system_cost': 91.00832493574674, 'generator_capacities': Generator
+OCGT         0.000000
+onwind     269.883584
+offwind    100.307709
+solar      225.552278
+Name: p_nom_opt, dtype: float64, 'storage_capacities': StorageUnit
+battery storage                 54.304140
+hydrogen storage underground    50.695647
 Name: p_nom_opt, dtype: float64, 'al_capacity': 6.050000000000001}</t>
         </is>
       </c>

--- a/examples/results/capacity_expansion_planning.xlsx
+++ b/examples/results/capacity_expansion_planning.xlsx
@@ -439,14 +439,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'p_min_pu': 0.1, 'system_cost': 84.40879288553354, 'generator_capacities': Generator
+          <t>{'p_min_pu': 0.1, 'system_cost': 6.8111435365222945, 'generator_capacities': Generator
 OCGT         0.000000
-onwind     273.893836
-offwind     90.992779
-solar      200.424159
+onwind     273.367505
+offwind     90.756446
+solar      201.150939
 Name: p_nom_opt, dtype: float64, 'storage_capacities': StorageUnit
-battery storage                 39.515823
-hydrogen storage underground    45.214748
+battery storage                 41.211722
+hydrogen storage underground    44.524970
 Name: p_nom_opt, dtype: float64, 'al_capacity': 6.050000000000001}</t>
         </is>
       </c>
@@ -457,32 +457,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'p_min_pu': 0.5, 'system_cost': 87.13052141396358, 'generator_capacities': Generator
+          <t>{'p_min_pu': 0.5, 'system_cost': 6.395316234390535, 'generator_capacities': Generator
 OCGT         0.000000
-onwind     262.030093
-offwind     96.068840
-solar      213.244300
+onwind     288.249425
+offwind     81.419666
+solar      205.947175
 Name: p_nom_opt, dtype: float64, 'storage_capacities': StorageUnit
-battery storage                 47.106483
-hydrogen storage underground    48.706380
+battery storage                 50.132036
+hydrogen storage underground    43.304166
 Name: p_nom_opt, dtype: float64, 'al_capacity': 6.050000000000001}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'p_min_pu': 0.9, 'system_cost': 91.00832493574674, 'generator_capacities': Generator
+          <t>{'p_min_pu': 0.88, 'system_cost': 6.221105551478686, 'generator_capacities': Generator
 OCGT         0.000000
-onwind     269.883584
-offwind    100.307709
-solar      225.552278
+onwind     274.749830
+offwind     86.775780
+solar      207.949649
 Name: p_nom_opt, dtype: float64, 'storage_capacities': StorageUnit
-battery storage                 54.304140
-hydrogen storage underground    50.695647
+battery storage                 48.584830
+hydrogen storage underground    43.998992
 Name: p_nom_opt, dtype: float64, 'al_capacity': 6.050000000000001}</t>
         </is>
       </c>
